--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="874" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4595E297-5266-43F0-9691-0DDC21599C9E}"/>
+  <xr:revisionPtr revIDLastSave="890" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D872AF1-A637-4C0A-B52F-655CA66845BC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4377,8 +4377,14 @@
       <c r="C224" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D224">
+        <v>3650</v>
+      </c>
+      <c r="E224">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>46277</v>
       </c>
@@ -4388,8 +4394,14 @@
       <c r="C225" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D225">
+        <v>1881</v>
+      </c>
+      <c r="E225">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>46278</v>
       </c>
@@ -4399,8 +4411,14 @@
       <c r="C226" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D226">
+        <v>4308</v>
+      </c>
+      <c r="E226">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>46279</v>
       </c>
@@ -4410,8 +4428,14 @@
       <c r="C227" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D227">
+        <v>2218</v>
+      </c>
+      <c r="E227">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>46280</v>
       </c>
@@ -4422,7 +4446,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>46281</v>
       </c>
@@ -4433,7 +4457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>46282</v>
       </c>
@@ -4444,7 +4468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>46283</v>
       </c>
@@ -4455,7 +4479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>46284</v>
       </c>
@@ -4466,7 +4490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>46285</v>
       </c>
@@ -4477,7 +4501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>46286</v>
       </c>
@@ -4488,7 +4512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>46287</v>
       </c>
@@ -4499,7 +4523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>46288</v>
       </c>
@@ -4510,7 +4534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>46289</v>
       </c>
@@ -4521,7 +4545,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>46290</v>
       </c>
@@ -4532,7 +4556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>46291</v>
       </c>
@@ -4543,7 +4567,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>46292</v>
       </c>
@@ -9383,6 +9407,12 @@
       <c r="C558" t="s">
         <v>19</v>
       </c>
+      <c r="D558">
+        <v>10876</v>
+      </c>
+      <c r="E558">
+        <v>141</v>
+      </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
@@ -9394,6 +9424,12 @@
       <c r="C559" t="s">
         <v>19</v>
       </c>
+      <c r="D559">
+        <v>10164</v>
+      </c>
+      <c r="E559">
+        <v>117</v>
+      </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
@@ -9405,8 +9441,14 @@
       <c r="C560" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D560">
+        <v>8403</v>
+      </c>
+      <c r="E560">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>46279</v>
       </c>
@@ -9416,8 +9458,14 @@
       <c r="C561" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D561">
+        <v>11244</v>
+      </c>
+      <c r="E561">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>46280</v>
       </c>
@@ -9428,7 +9476,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>46281</v>
       </c>
@@ -9439,7 +9487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>46282</v>
       </c>
@@ -9450,7 +9498,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>46283</v>
       </c>
@@ -9461,7 +9509,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>46284</v>
       </c>
@@ -9472,7 +9520,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>46285</v>
       </c>
@@ -9483,7 +9531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>46286</v>
       </c>
@@ -9494,7 +9542,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>46287</v>
       </c>
@@ -9505,7 +9553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>46288</v>
       </c>
@@ -9516,7 +9564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>46289</v>
       </c>
@@ -9527,7 +9575,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>46290</v>
       </c>
@@ -9538,7 +9586,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>46291</v>
       </c>
@@ -9549,7 +9597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>46292</v>
       </c>
@@ -9560,7 +9608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>46293</v>
       </c>
@@ -9571,7 +9619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>46294</v>
       </c>
@@ -13624,6 +13672,12 @@
       <c r="C847" t="s">
         <v>18</v>
       </c>
+      <c r="D847">
+        <v>133.33333400000001</v>
+      </c>
+      <c r="E847">
+        <v>8</v>
+      </c>
     </row>
     <row r="848" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A848" s="1">
@@ -13635,8 +13689,14 @@
       <c r="C848" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D848">
+        <v>2862.5</v>
+      </c>
+      <c r="E848">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="849" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A849" s="1">
         <v>46278</v>
       </c>
@@ -13646,8 +13706,14 @@
       <c r="C849" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D849">
+        <v>0</v>
+      </c>
+      <c r="E849">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A850" s="1">
         <v>46279</v>
       </c>
@@ -13657,8 +13723,14 @@
       <c r="C850" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D850">
+        <v>285.42</v>
+      </c>
+      <c r="E850">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="851" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A851" s="1">
         <v>46280</v>
       </c>
@@ -13669,7 +13741,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="852" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A852" s="1">
         <v>46281</v>
       </c>
@@ -13680,7 +13752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="853" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A853" s="1">
         <v>46282</v>
       </c>
@@ -13691,7 +13763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="854" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A854" s="1">
         <v>46283</v>
       </c>
@@ -13702,7 +13774,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="855" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A855" s="1">
         <v>46284</v>
       </c>
@@ -13713,7 +13785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="856" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A856" s="1">
         <v>46285</v>
       </c>
@@ -13724,7 +13796,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="857" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A857" s="1">
         <v>46286</v>
       </c>
@@ -13735,7 +13807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="858" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A858" s="1">
         <v>46287</v>
       </c>
@@ -13746,7 +13818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="859" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A859" s="1">
         <v>46288</v>
       </c>
@@ -13757,7 +13829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="860" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A860" s="1">
         <v>46289</v>
       </c>
@@ -13768,7 +13840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="861" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A861" s="1">
         <v>46290</v>
       </c>
@@ -13779,7 +13851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="862" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A862" s="1">
         <v>46291</v>
       </c>
@@ -13790,7 +13862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="863" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A863" s="1">
         <v>46292</v>
       </c>
@@ -13801,7 +13873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="864" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A864" s="1">
         <v>46293</v>
       </c>
@@ -17865,8 +17937,14 @@
       <c r="C1136" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1136">
+        <v>6919.6833360000001</v>
+      </c>
+      <c r="E1136">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1137" s="1">
         <v>46277</v>
       </c>
@@ -17876,8 +17954,14 @@
       <c r="C1137" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1137">
+        <v>2959.6400000000003</v>
+      </c>
+      <c r="E1137">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1138" s="1">
         <v>46278</v>
       </c>
@@ -17887,8 +17971,14 @@
       <c r="C1138" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1138">
+        <v>0</v>
+      </c>
+      <c r="E1138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1139" s="1">
         <v>46279</v>
       </c>
@@ -17898,8 +17988,14 @@
       <c r="C1139" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1139">
+        <v>1478.7500030000001</v>
+      </c>
+      <c r="E1139">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1140" s="1">
         <v>46280</v>
       </c>
@@ -17910,7 +18006,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1141" s="1">
         <v>46281</v>
       </c>
@@ -17921,7 +18017,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1142" s="1">
         <v>46282</v>
       </c>
@@ -17932,7 +18028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1143" s="1">
         <v>46283</v>
       </c>
@@ -17943,7 +18039,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1144" s="1">
         <v>46284</v>
       </c>
@@ -17954,7 +18050,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1145" s="1">
         <v>46285</v>
       </c>
@@ -17965,7 +18061,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1146" s="1">
         <v>46286</v>
       </c>
@@ -17976,7 +18072,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1147" s="1">
         <v>46287</v>
       </c>
@@ -17987,7 +18083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1148" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1148" s="1">
         <v>46288</v>
       </c>
@@ -17998,7 +18094,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1149" s="1">
         <v>46289</v>
       </c>
@@ -18009,7 +18105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1150" s="1">
         <v>46290</v>
       </c>
@@ -18020,7 +18116,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1151" s="1">
         <v>46291</v>
       </c>
@@ -18031,7 +18127,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1152" s="1">
         <v>46292</v>
       </c>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="890" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D872AF1-A637-4C0A-B52F-655CA66845BC}"/>
+  <xr:revisionPtr revIDLastSave="898" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E742AB-499E-4971-8665-7AE948FA664A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4445,6 +4445,12 @@
       <c r="C228" t="s">
         <v>18</v>
       </c>
+      <c r="D228">
+        <v>2326</v>
+      </c>
+      <c r="E228">
+        <v>28</v>
+      </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
@@ -9475,6 +9481,12 @@
       <c r="C562" t="s">
         <v>19</v>
       </c>
+      <c r="D562">
+        <v>7553</v>
+      </c>
+      <c r="E562">
+        <v>86</v>
+      </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
@@ -13740,6 +13752,12 @@
       <c r="C851" t="s">
         <v>18</v>
       </c>
+      <c r="D851">
+        <v>405.14166899999998</v>
+      </c>
+      <c r="E851">
+        <v>10</v>
+      </c>
     </row>
     <row r="852" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A852" s="1">
@@ -18004,6 +18022,12 @@
       </c>
       <c r="C1140" t="s">
         <v>19</v>
+      </c>
+      <c r="D1140">
+        <v>3727.3333379999999</v>
+      </c>
+      <c r="E1140">
+        <v>33</v>
       </c>
     </row>
     <row r="1141" spans="1:5" x14ac:dyDescent="0.35">
@@ -42179,6 +42203,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
@@ -42187,15 +42220,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42422,20 +42446,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
     <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="898" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E742AB-499E-4971-8665-7AE948FA664A}"/>
+  <xr:revisionPtr revIDLastSave="906" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA9DDD8B-C2C2-44C1-8466-7C6F2DA57A4B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4462,6 +4462,12 @@
       <c r="C229" t="s">
         <v>18</v>
       </c>
+      <c r="D229">
+        <v>3366</v>
+      </c>
+      <c r="E229">
+        <v>45</v>
+      </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
@@ -9498,6 +9504,12 @@
       <c r="C563" t="s">
         <v>19</v>
       </c>
+      <c r="D563">
+        <v>8586</v>
+      </c>
+      <c r="E563">
+        <v>90</v>
+      </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
@@ -13769,6 +13781,12 @@
       <c r="C852" t="s">
         <v>18</v>
       </c>
+      <c r="D852">
+        <v>589.20833400000004</v>
+      </c>
+      <c r="E852">
+        <v>11</v>
+      </c>
     </row>
     <row r="853" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A853" s="1">
@@ -18039,6 +18057,12 @@
       </c>
       <c r="C1141" t="s">
         <v>19</v>
+      </c>
+      <c r="D1141">
+        <v>2669.1666730000002</v>
+      </c>
+      <c r="E1141">
+        <v>63</v>
       </c>
     </row>
     <row r="1142" spans="1:5" x14ac:dyDescent="0.35">
@@ -42212,17 +42236,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42445,6 +42458,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
   <ds:schemaRefs>
@@ -42454,17 +42478,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42483,6 +42496,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="906" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA9DDD8B-C2C2-44C1-8466-7C6F2DA57A4B}"/>
+  <xr:revisionPtr revIDLastSave="914" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51D7BF48-5131-430B-B990-20930B9E4412}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -4479,6 +4479,12 @@
       <c r="C230" t="s">
         <v>18</v>
       </c>
+      <c r="D230">
+        <v>1609</v>
+      </c>
+      <c r="E230">
+        <v>21</v>
+      </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
@@ -9521,6 +9527,12 @@
       <c r="C564" t="s">
         <v>19</v>
       </c>
+      <c r="D564">
+        <v>9148</v>
+      </c>
+      <c r="E564">
+        <v>98</v>
+      </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
@@ -13798,6 +13810,12 @@
       <c r="C853" t="s">
         <v>18</v>
       </c>
+      <c r="D853">
+        <v>2346.1833390000002</v>
+      </c>
+      <c r="E853">
+        <v>34</v>
+      </c>
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A854" s="1">
@@ -18074,6 +18092,12 @@
       </c>
       <c r="C1142" t="s">
         <v>19</v>
+      </c>
+      <c r="D1142">
+        <v>5801.7750340000002</v>
+      </c>
+      <c r="E1142">
+        <v>67</v>
       </c>
     </row>
     <row r="1143" spans="1:5" x14ac:dyDescent="0.35">
@@ -42236,6 +42260,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42458,17 +42493,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
   <ds:schemaRefs>
@@ -42478,6 +42502,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42496,17 +42531,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="914" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51D7BF48-5131-430B-B990-20930B9E4412}"/>
+  <xr:revisionPtr revIDLastSave="922" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{540A5574-8D11-4542-94D8-85BAC55623E2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -4496,6 +4496,12 @@
       <c r="C231" t="s">
         <v>18</v>
       </c>
+      <c r="D231">
+        <v>3526</v>
+      </c>
+      <c r="E231">
+        <v>53</v>
+      </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
@@ -4507,6 +4513,12 @@
       <c r="C232" t="s">
         <v>18</v>
       </c>
+      <c r="D232">
+        <v>16857</v>
+      </c>
+      <c r="E232">
+        <v>29</v>
+      </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
@@ -4518,6 +4530,12 @@
       <c r="C233" t="s">
         <v>18</v>
       </c>
+      <c r="D233">
+        <v>7165</v>
+      </c>
+      <c r="E233">
+        <v>64</v>
+      </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
@@ -9544,6 +9562,12 @@
       <c r="C565" t="s">
         <v>19</v>
       </c>
+      <c r="D565">
+        <v>3526</v>
+      </c>
+      <c r="E565">
+        <v>122</v>
+      </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
@@ -9555,6 +9579,12 @@
       <c r="C566" t="s">
         <v>19</v>
       </c>
+      <c r="D566">
+        <v>2075</v>
+      </c>
+      <c r="E566">
+        <v>150</v>
+      </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
@@ -9566,6 +9596,12 @@
       <c r="C567" t="s">
         <v>19</v>
       </c>
+      <c r="D567">
+        <v>4575</v>
+      </c>
+      <c r="E567">
+        <v>73</v>
+      </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
@@ -13827,6 +13863,12 @@
       <c r="C854" t="s">
         <v>18</v>
       </c>
+      <c r="D854">
+        <v>420.83333599999997</v>
+      </c>
+      <c r="E854">
+        <v>10</v>
+      </c>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A855" s="1">
@@ -13838,6 +13880,12 @@
       <c r="C855" t="s">
         <v>18</v>
       </c>
+      <c r="D855">
+        <v>1624.94</v>
+      </c>
+      <c r="E855">
+        <v>21</v>
+      </c>
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A856" s="1">
@@ -13849,6 +13897,12 @@
       <c r="C856" t="s">
         <v>18</v>
       </c>
+      <c r="D856">
+        <v>0</v>
+      </c>
+      <c r="E856">
+        <v>0</v>
+      </c>
     </row>
     <row r="857" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A857" s="1">
@@ -18110,6 +18164,12 @@
       <c r="C1143" t="s">
         <v>19</v>
       </c>
+      <c r="D1143">
+        <v>9754.2499989999997</v>
+      </c>
+      <c r="E1143">
+        <v>173</v>
+      </c>
     </row>
     <row r="1144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1144" s="1">
@@ -18121,6 +18181,12 @@
       <c r="C1144" t="s">
         <v>19</v>
       </c>
+      <c r="D1144">
+        <v>3987.4416759999999</v>
+      </c>
+      <c r="E1144">
+        <v>71</v>
+      </c>
     </row>
     <row r="1145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1145" s="1">
@@ -18131,6 +18197,12 @@
       </c>
       <c r="C1145" t="s">
         <v>19</v>
+      </c>
+      <c r="D1145">
+        <v>0</v>
+      </c>
+      <c r="E1145">
+        <v>0</v>
       </c>
     </row>
     <row r="1146" spans="1:5" x14ac:dyDescent="0.35">
@@ -42251,26 +42323,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42493,26 +42545,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42531,6 +42584,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="922" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{540A5574-8D11-4542-94D8-85BAC55623E2}"/>
+  <xr:revisionPtr revIDLastSave="930" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96AF8E9C-B0C5-4318-94CE-18E44B427B87}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4547,6 +4547,12 @@
       <c r="C234" t="s">
         <v>18</v>
       </c>
+      <c r="D234">
+        <v>2213</v>
+      </c>
+      <c r="E234">
+        <v>30</v>
+      </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
@@ -9613,6 +9619,12 @@
       <c r="C568" t="s">
         <v>19</v>
       </c>
+      <c r="D568">
+        <v>12164</v>
+      </c>
+      <c r="E568">
+        <v>131</v>
+      </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
@@ -13914,6 +13926,12 @@
       <c r="C857" t="s">
         <v>18</v>
       </c>
+      <c r="D857">
+        <v>455.00000499999999</v>
+      </c>
+      <c r="E857">
+        <v>10</v>
+      </c>
     </row>
     <row r="858" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A858" s="1">
@@ -18214,6 +18232,12 @@
       </c>
       <c r="C1146" t="s">
         <v>19</v>
+      </c>
+      <c r="D1146">
+        <v>2083.0833360000001</v>
+      </c>
+      <c r="E1146">
+        <v>35</v>
       </c>
     </row>
     <row r="1147" spans="1:5" x14ac:dyDescent="0.35">
@@ -42546,6 +42570,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
@@ -42554,15 +42587,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42585,6 +42609,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -42595,14 +42627,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="930" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96AF8E9C-B0C5-4318-94CE-18E44B427B87}"/>
+  <xr:revisionPtr revIDLastSave="938" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F67946-10BC-40B0-86B9-2D8CA272DC51}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -4564,6 +4564,12 @@
       <c r="C235" t="s">
         <v>18</v>
       </c>
+      <c r="D235">
+        <v>3480</v>
+      </c>
+      <c r="E235">
+        <v>52</v>
+      </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
@@ -9636,6 +9642,12 @@
       <c r="C569" t="s">
         <v>19</v>
       </c>
+      <c r="D569">
+        <v>12334</v>
+      </c>
+      <c r="E569">
+        <v>126</v>
+      </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
@@ -13943,6 +13955,12 @@
       <c r="C858" t="s">
         <v>18</v>
       </c>
+      <c r="D858">
+        <v>2740.833341</v>
+      </c>
+      <c r="E858">
+        <v>27</v>
+      </c>
     </row>
     <row r="859" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A859" s="1">
@@ -18249,6 +18267,12 @@
       </c>
       <c r="C1147" t="s">
         <v>19</v>
+      </c>
+      <c r="D1147">
+        <v>5727.583337</v>
+      </c>
+      <c r="E1147">
+        <v>65</v>
       </c>
     </row>
     <row r="1148" spans="1:5" x14ac:dyDescent="0.35">
@@ -42347,6 +42371,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42569,27 +42613,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42608,25 +42651,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="938" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F67946-10BC-40B0-86B9-2D8CA272DC51}"/>
+  <xr:revisionPtr revIDLastSave="946" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54C8FAA4-0DD0-4E4B-8F59-1E7E24F41818}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57AC4B45-296A-4D46-AAD5-7774D814CF2E}" name="Revenue_Daily" displayName="Revenue_Daily" ref="A1:E1247" totalsRowShown="0">
   <autoFilter ref="A1:E1247" xr:uid="{57AC4B45-296A-4D46-AAD5-7774D814CF2E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{492A6730-A96D-4C72-8BB4-18626BD2E7E5}" name="Date" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{492A6730-A96D-4C72-8BB4-18626BD2E7E5}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{CDB14195-0D89-4EF9-944D-048BFDF2D9F9}" name="Outlet"/>
     <tableColumn id="3" xr3:uid="{5125995A-2E61-4292-B916-B5810FA9C618}" name="Meal Period"/>
     <tableColumn id="4" xr3:uid="{4149D570-795C-4EB8-9808-7A51F3D19297}" name="Revenue"/>
@@ -205,7 +205,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69BB017A-8340-44F6-9A98-F8635ECB1801}" name="Budget" displayName="Budget" ref="A1:E1337" totalsRowShown="0">
   <autoFilter ref="A1:E1337" xr:uid="{69BB017A-8340-44F6-9A98-F8635ECB1801}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C24C951D-52F6-40AF-9163-642AD07B99DC}" name="Date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C24C951D-52F6-40AF-9163-642AD07B99DC}" name="Date" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{3E8EEB24-E11D-485D-9434-9A86E32F3C78}" name="Outlet"/>
     <tableColumn id="3" xr3:uid="{3A9362A6-D763-4998-BC01-BDB0BE8D1A39}" name="Meal Period"/>
     <tableColumn id="4" xr3:uid="{402E61B1-84A6-47A1-90F7-F213A51D32D9}" name="Revenue Budget"/>
@@ -4581,6 +4581,12 @@
       <c r="C236" t="s">
         <v>18</v>
       </c>
+      <c r="D236">
+        <v>2841</v>
+      </c>
+      <c r="E236">
+        <v>32</v>
+      </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
@@ -9659,6 +9665,12 @@
       <c r="C570" t="s">
         <v>19</v>
       </c>
+      <c r="D570">
+        <v>28801</v>
+      </c>
+      <c r="E570">
+        <v>195</v>
+      </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
@@ -13972,6 +13984,12 @@
       <c r="C859" t="s">
         <v>18</v>
       </c>
+      <c r="D859">
+        <v>2490.8333389999998</v>
+      </c>
+      <c r="E859">
+        <v>32</v>
+      </c>
     </row>
     <row r="860" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A860" s="1">
@@ -18284,6 +18302,12 @@
       </c>
       <c r="C1148" t="s">
         <v>19</v>
+      </c>
+      <c r="D1148">
+        <v>2168.8416699999998</v>
+      </c>
+      <c r="E1148">
+        <v>43</v>
       </c>
     </row>
     <row r="1149" spans="1:5" x14ac:dyDescent="0.35">
@@ -42382,15 +42406,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42613,6 +42628,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
@@ -42625,14 +42649,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42651,6 +42667,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="946" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54C8FAA4-0DD0-4E4B-8F59-1E7E24F41818}"/>
+  <xr:revisionPtr revIDLastSave="954" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36F42175-4FFC-447B-8527-0D8B72FF2C4A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -191,7 +191,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57AC4B45-296A-4D46-AAD5-7774D814CF2E}" name="Revenue_Daily" displayName="Revenue_Daily" ref="A1:E1247" totalsRowShown="0">
   <autoFilter ref="A1:E1247" xr:uid="{57AC4B45-296A-4D46-AAD5-7774D814CF2E}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{492A6730-A96D-4C72-8BB4-18626BD2E7E5}" name="Date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{492A6730-A96D-4C72-8BB4-18626BD2E7E5}" name="Date" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{CDB14195-0D89-4EF9-944D-048BFDF2D9F9}" name="Outlet"/>
     <tableColumn id="3" xr3:uid="{5125995A-2E61-4292-B916-B5810FA9C618}" name="Meal Period"/>
     <tableColumn id="4" xr3:uid="{4149D570-795C-4EB8-9808-7A51F3D19297}" name="Revenue"/>
@@ -205,7 +205,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{69BB017A-8340-44F6-9A98-F8635ECB1801}" name="Budget" displayName="Budget" ref="A1:E1337" totalsRowShown="0">
   <autoFilter ref="A1:E1337" xr:uid="{69BB017A-8340-44F6-9A98-F8635ECB1801}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C24C951D-52F6-40AF-9163-642AD07B99DC}" name="Date" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{C24C951D-52F6-40AF-9163-642AD07B99DC}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{3E8EEB24-E11D-485D-9434-9A86E32F3C78}" name="Outlet"/>
     <tableColumn id="3" xr3:uid="{3A9362A6-D763-4998-BC01-BDB0BE8D1A39}" name="Meal Period"/>
     <tableColumn id="4" xr3:uid="{402E61B1-84A6-47A1-90F7-F213A51D32D9}" name="Revenue Budget"/>
@@ -4598,6 +4598,12 @@
       <c r="C237" t="s">
         <v>18</v>
       </c>
+      <c r="D237">
+        <v>7822</v>
+      </c>
+      <c r="E237">
+        <v>64</v>
+      </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
@@ -9682,6 +9688,12 @@
       <c r="C571" t="s">
         <v>19</v>
       </c>
+      <c r="D571">
+        <v>24207</v>
+      </c>
+      <c r="E571">
+        <v>200</v>
+      </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
@@ -14001,6 +14013,12 @@
       <c r="C860" t="s">
         <v>18</v>
       </c>
+      <c r="D860">
+        <v>1120.458343</v>
+      </c>
+      <c r="E860">
+        <v>21</v>
+      </c>
     </row>
     <row r="861" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A861" s="1">
@@ -18319,6 +18337,12 @@
       </c>
       <c r="C1149" t="s">
         <v>19</v>
+      </c>
+      <c r="D1149">
+        <v>4724.9166640000003</v>
+      </c>
+      <c r="E1149">
+        <v>56</v>
       </c>
     </row>
     <row r="1150" spans="1:5" x14ac:dyDescent="0.35">
@@ -42395,14 +42419,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42629,21 +42651,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -42668,9 +42689,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
